--- a/data/lca_database.xlsx
+++ b/data/lca_database.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vub.sharepoint.com/sites/ORG-FacIR/EVERGi/RepositoryNEW/04. Projects/Ecoscore/Ecoscore 2.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DERLL\Documents\MA1\Q2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="798" documentId="8_{B3F68064-797A-4D14-9B82-C10989F11121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7DF6468-170B-415C-B9F4-9BAAC14B880D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F34FDBF-D05A-481C-B4DF-3954796C131E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Emission factor" sheetId="1" r:id="rId1"/>
     <sheet name="Car parameters" sheetId="2" r:id="rId2"/>
-    <sheet name="Results" sheetId="3" r:id="rId3"/>
-    <sheet name="Example of graphs" sheetId="4" r:id="rId4"/>
-    <sheet name="Infopages" sheetId="6" r:id="rId5"/>
+    <sheet name="Car parameters v2" sheetId="7" r:id="rId3"/>
+    <sheet name="Results" sheetId="3" r:id="rId4"/>
+    <sheet name="Example of graphs" sheetId="4" r:id="rId5"/>
+    <sheet name="Infopages" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="140">
   <si>
     <t>unit</t>
   </si>
@@ -395,6 +396,96 @@
   </si>
   <si>
     <t>Here it is the sum, per km</t>
+  </si>
+  <si>
+    <t>tyre_wear</t>
+  </si>
+  <si>
+    <t>brake_wear</t>
+  </si>
+  <si>
+    <t>Tyre wear</t>
+  </si>
+  <si>
+    <t>Brake wear</t>
+  </si>
+  <si>
+    <t>=TTW in parameters + tyre_wear*Tyre wear+brake_wear*brake wear</t>
+  </si>
+  <si>
+    <t>=tyre_wear*Tyre wear+brake_wear*brake wear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario description to be added as additional information </t>
+  </si>
+  <si>
+    <t>The fuel consumption and CO2 emissions correspond to the results from the homologation tests</t>
+  </si>
+  <si>
+    <t>The fuel consumption and CO2 emissions correspond to the real-life consumption, adapting the utility factor of the PHEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petrol </t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to name the fuel type to be better understand : </t>
+  </si>
+  <si>
+    <t>Petrol hybrid</t>
+  </si>
+  <si>
+    <t>Petrol plugin hybrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrogen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The electricity mix corresponds to the assumed future 2050 Belgium mix </t>
+  </si>
+  <si>
+    <t>Prospective electricity mix</t>
+  </si>
+  <si>
+    <t>The electricity mix is assessed dynamically and it corresponds to the Belgium prospective mix. It means that it represents the average impacts of the electricity mix up until the end of the vehicle usage. It therefore includes the fact that the electricity mix is expected to decrease during the use of the car.</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New name </t>
+  </si>
+  <si>
+    <r>
+      <t>Grey hydrogen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is produced by reforming methane with steam which is the dominant method today.  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Green hydrogen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is produced by electrolysis of water, powered entirely by renewable electricity (solar, wind, etc.). </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -424,7 +515,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,6 +525,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,7 +708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -650,9 +759,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -668,10 +774,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -681,6 +783,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -690,8 +805,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -705,16 +820,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -729,7 +835,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1970,8 +2084,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="69" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
@@ -3003,7 +3117,7 @@
         <v>4.0104985149864474</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -3065,7 +3179,7 @@
         <v>0.54315536049582447</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -3127,7 +3241,7 @@
         <v>1.8355167734903679</v>
       </c>
     </row>
-    <row r="19" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>23</v>
       </c>
@@ -3189,20 +3303,151 @@
         <v>116.228145054499</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-4.6635996822953267E-2</v>
+      </c>
+      <c r="G20" s="2">
+        <v>-881.35460438045925</v>
+      </c>
+      <c r="H20" s="2">
+        <v>-881.35046762429397</v>
+      </c>
+      <c r="I20" s="2">
+        <v>-4.1367561653779528E-3</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>-7.016642740788559E-3</v>
+      </c>
+      <c r="L20" s="2">
+        <v>-6.215999932974569E-5</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>-5.6421028569052207E-8</v>
+      </c>
+      <c r="O20" s="2">
+        <v>-2.294189675815847E-5</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
+        <v>-1.256627216299778E-4</v>
+      </c>
+      <c r="U20" s="2">
+        <v>-2.8871599981749041E-3</v>
+      </c>
+      <c r="V20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-6.405899696572126E-4</v>
+      </c>
+      <c r="G21" s="2">
+        <v>-36.370534160283107</v>
+      </c>
+      <c r="H21" s="2">
+        <v>-35.597807087931578</v>
+      </c>
+      <c r="I21" s="2">
+        <v>-0.77272707235152915</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>-1.0524964663104969E-3</v>
+      </c>
+      <c r="L21" s="2">
+        <v>-2.895639982971027E-4</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>-2.8286208082438391E-9</v>
+      </c>
+      <c r="O21" s="2">
+        <v>-1.2676540907787611E-6</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <v>-1.3054947063404359E-5</v>
+      </c>
+      <c r="U21" s="2">
+        <v>-3.9657900798125562E-5</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3211,23 +3456,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEACA5F-E072-417D-8DE7-0C8FAD7D83DE}">
-  <dimension ref="A1:O132"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R92"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="51.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.44140625" customWidth="1"/>
     <col min="3" max="4" width="27.21875" customWidth="1"/>
     <col min="5" max="5" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
@@ -3268,22 +3520,28 @@
       <c r="O1" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q1" s="35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="38" t="s">
-        <v>36</v>
+      <c r="B2" s="40" t="s">
+        <v>127</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="41">
         <v>200000</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="41">
         <v>260000</v>
       </c>
       <c r="G2">
@@ -3314,16 +3572,23 @@
       <c r="O2" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" s="5">
+        <v>-1.7E-5</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>-1.26E-5</v>
+      </c>
+      <c r="R2" s="36"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="38"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
       <c r="G3" s="2">
         <v>1552</v>
       </c>
@@ -3351,16 +3616,23 @@
       <c r="O3" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" s="5">
+        <v>-1.9700000000000001E-5</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>-1.5299999999999999E-5</v>
+      </c>
+      <c r="R3" s="36"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="38"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
       <c r="G4" s="2">
         <v>1876</v>
       </c>
@@ -3388,18 +3660,25 @@
       <c r="O4" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" s="5">
+        <v>-2.0999999999999999E-5</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>-1.6500000000000001E-5</v>
+      </c>
+      <c r="R4" s="36"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="40" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
       <c r="G5" s="7">
         <v>1270</v>
       </c>
@@ -3428,16 +3707,23 @@
       <c r="O5" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" s="5">
+        <v>-1.7200000000000001E-5</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>-1.29E-5</v>
+      </c>
+      <c r="R5" s="36"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="38"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
       <c r="G6" s="2">
         <v>1583</v>
       </c>
@@ -3465,16 +3751,23 @@
       <c r="O6" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" s="5">
+        <v>-1.9899999999999999E-5</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>-1.5400000000000002E-5</v>
+      </c>
+      <c r="R6" s="36"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="38"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
       <c r="G7" s="2">
         <v>1828</v>
       </c>
@@ -3502,18 +3795,25 @@
       <c r="O7" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="5">
+        <v>-2.12E-5</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>-1.66E-5</v>
+      </c>
+      <c r="R7" s="36"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="40" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
       <c r="G8" s="2">
         <v>1256</v>
       </c>
@@ -3541,16 +3841,23 @@
       <c r="O8" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" s="5">
+        <v>-1.6699999999999999E-5</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>-1.24E-5</v>
+      </c>
+      <c r="R8" s="36"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
       <c r="G9" s="2">
         <v>1434</v>
       </c>
@@ -3578,16 +3885,23 @@
       <c r="O9" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" s="5">
+        <v>-1.9000000000000001E-5</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>-1.5E-5</v>
+      </c>
+      <c r="R9" s="36"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="38"/>
+      <c r="B10" s="40"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
       <c r="G10" s="2">
         <v>1515</v>
       </c>
@@ -3615,18 +3929,25 @@
       <c r="O10" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="5">
+        <v>-4.1199999999999999E-5</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>-1.66E-5</v>
+      </c>
+      <c r="R10" s="36"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="40" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
       <c r="G11" s="2">
         <v>1165</v>
       </c>
@@ -3654,16 +3975,22 @@
       <c r="O11" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" s="5">
+        <v>-1.7E-5</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>-1.26E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="38"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="2">
         <v>1503</v>
       </c>
@@ -3691,16 +4018,22 @@
       <c r="O12" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" s="5">
+        <v>-1.9700000000000001E-5</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>-1.5299999999999999E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="38"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
       <c r="G13" s="2">
         <v>0</v>
       </c>
@@ -3728,18 +4061,24 @@
       <c r="O13" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" s="5">
+        <v>-2.0999999999999999E-5</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>-1.6500000000000001E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="40" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
       <c r="G14" s="7">
         <v>1233</v>
       </c>
@@ -3767,16 +4106,23 @@
       <c r="O14" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" s="5">
+        <v>-1.7200000000000001E-5</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>-6.8499999999999996E-6</v>
+      </c>
+      <c r="R14" s="36"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="38"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="2">
         <v>1530</v>
       </c>
@@ -3805,16 +4151,23 @@
       <c r="O15" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="5">
+        <v>-2.02E-5</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>-8.4999999999999999E-6</v>
+      </c>
+      <c r="R15" s="36"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="38"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="2">
         <v>2197</v>
       </c>
@@ -3842,20 +4195,27 @@
       <c r="O16" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" s="5">
+        <v>-2.1299999999999999E-5</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>-9.1500000000000005E-6</v>
+      </c>
+      <c r="R16" s="36"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
       <c r="G17" s="2">
         <v>1678</v>
       </c>
@@ -3884,16 +4244,23 @@
       <c r="O17" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" s="5">
+        <v>-1.8E-5</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>-7.1999999999999997E-6</v>
+      </c>
+      <c r="R17" s="36"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
       <c r="G18" s="2">
         <v>1880</v>
       </c>
@@ -3922,16 +4289,23 @@
       <c r="O18" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" s="5">
+        <v>-2.09E-5</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>-8.8699999999999998E-6</v>
+      </c>
+      <c r="R18" s="36"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
       <c r="G19" s="2">
         <v>2234</v>
       </c>
@@ -3959,18 +4333,25 @@
       <c r="O19" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19" s="5">
+        <v>-2.26E-5</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>-9.9199999999999999E-6</v>
+      </c>
+      <c r="R19" s="36"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="35" t="s">
+      <c r="B20" s="42"/>
+      <c r="C20" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
       <c r="G20" s="2">
         <v>1678</v>
       </c>
@@ -3999,16 +4380,23 @@
       <c r="O20" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20" s="5">
+        <v>-1.8E-5</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>-7.1999999999999997E-6</v>
+      </c>
+      <c r="R20" s="36"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
       <c r="G21" s="2">
         <v>1880</v>
       </c>
@@ -4037,16 +4425,23 @@
       <c r="O21" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21" s="5">
+        <v>-2.09E-5</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>-8.8699999999999998E-6</v>
+      </c>
+      <c r="R21" s="36"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
       <c r="G22" s="2">
         <v>2234</v>
       </c>
@@ -4074,20 +4469,27 @@
       <c r="O22" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P22" s="5">
+        <v>-2.26E-5</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>-9.9199999999999999E-6</v>
+      </c>
+      <c r="R22" s="36"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
       <c r="G23" s="7">
         <v>1528</v>
       </c>
@@ -4115,16 +4517,22 @@
       <c r="O23" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P23" s="5">
+        <v>-1.7900000000000001E-5</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>-6.7800000000000003E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
       <c r="G24" s="2">
         <v>2025</v>
       </c>
@@ -4153,16 +4561,22 @@
       <c r="O24" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24" s="5">
+        <v>-2.09E-5</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>-8.5099999999999998E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
       <c r="G25" s="2">
         <v>2469</v>
       </c>
@@ -4190,25 +4604,31 @@
       <c r="O25" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P25" s="5">
+        <v>-2.1800000000000001E-5</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>-9.0299999999999999E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="35">
+      <c r="B26" s="42"/>
+      <c r="C26" s="41">
         <v>2050</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
       <c r="G26" s="7">
         <v>1528</v>
       </c>
       <c r="H26" s="7">
         <v>47</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="31">
         <v>265</v>
       </c>
       <c r="J26" s="7">
@@ -4229,16 +4649,23 @@
       <c r="O26" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P26" s="5">
+        <v>-1.7900000000000001E-5</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>-6.7800000000000003E-6</v>
+      </c>
+      <c r="R26" s="36"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
       <c r="G27" s="2">
         <v>2025</v>
       </c>
@@ -4267,16 +4694,23 @@
       <c r="O27" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27" s="5">
+        <v>-2.09E-5</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>-8.5099999999999998E-6</v>
+      </c>
+      <c r="R27" s="36"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
       <c r="G28" s="2">
         <v>2469</v>
       </c>
@@ -4304,30 +4738,37 @@
       <c r="O28" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P28" s="5">
+        <v>-2.1800000000000001E-5</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>-9.0299999999999999E-6</v>
+      </c>
+      <c r="R28" s="36"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="51">
-        <v>0</v>
-      </c>
-      <c r="H29" s="51">
-        <v>0</v>
-      </c>
-      <c r="I29" s="51">
-        <v>0</v>
-      </c>
-      <c r="J29" s="51">
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="7">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7">
         <v>0</v>
       </c>
       <c r="K29" s="2">
@@ -4345,16 +4786,23 @@
       <c r="O29" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P29" s="5">
+        <v>-1.7200000000000001E-5</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>-6.4300000000000003E-6</v>
+      </c>
+      <c r="R29" s="36"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
       <c r="G30" s="2">
         <v>1800</v>
       </c>
@@ -4383,16 +4831,23 @@
       <c r="O30" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P30" s="5">
+        <v>-2.0800000000000001E-5</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>-8.4200000000000007E-6</v>
+      </c>
+      <c r="R30" s="36"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
       <c r="G31" s="2">
         <v>0</v>
       </c>
@@ -4420,28 +4875,35 @@
       <c r="O31" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P31" s="5">
+        <v>-2.23E-5</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>-9.3300000000000005E-6</v>
+      </c>
+      <c r="R31" s="36"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="36"/>
-      <c r="C32" s="35" t="s">
+      <c r="B32" s="42"/>
+      <c r="C32" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="51">
-        <v>0</v>
-      </c>
-      <c r="H32" s="51">
-        <v>0</v>
-      </c>
-      <c r="I32" s="51">
-        <v>0</v>
-      </c>
-      <c r="J32" s="51">
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="7">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7">
         <v>0</v>
       </c>
       <c r="K32" s="2">
@@ -4459,16 +4921,23 @@
       <c r="O32" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32" s="5">
+        <v>-1.7200000000000001E-5</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>-6.4300000000000003E-6</v>
+      </c>
+      <c r="R32" s="36"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
       <c r="G33" s="2">
         <v>1800</v>
       </c>
@@ -4497,16 +4966,23 @@
       <c r="O33" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P33" s="5">
+        <v>-2.0800000000000001E-5</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>-8.4200000000000007E-6</v>
+      </c>
+      <c r="R33" s="36"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
       <c r="G34" s="2">
         <v>0</v>
       </c>
@@ -4534,66 +5010,68 @@
       <c r="O34" s="5">
         <v>1.0752688172043E-5</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P34" s="5">
+        <v>-2.23E-5</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>-9.3300000000000005E-6</v>
+      </c>
+      <c r="R34" s="36"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D35" s="12"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="132" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
-      <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="3"/>
-      <c r="J132" s="3"/>
-      <c r="K132" s="3"/>
+    <row r="92" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E2:E34"/>
-    <mergeCell ref="F2:F34"/>
-    <mergeCell ref="D2:D34"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="C32:C34"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="B29:B34"/>
     <mergeCell ref="B23:B28"/>
@@ -4602,6 +5080,11 @@
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="B14:B16"/>
+    <mergeCell ref="E2:E34"/>
+    <mergeCell ref="F2:F34"/>
+    <mergeCell ref="D2:D34"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C34"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C26:C28"/>
@@ -4612,9 +5095,1517 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298AA890-4968-4ADA-999E-24F3FFBEE94B}">
+  <dimension ref="A1:S34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="R1" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="2">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="E2" s="2">
+        <v>5.7766708249443497E-5</v>
+      </c>
+      <c r="F2" s="2">
+        <v>7.0653775245254323E-4</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2.724731842799398E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.1590160371398489E-6</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1.9429462130907331E-12</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2.8989820149356931E-11</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>4.5867635272107989E-10</v>
+      </c>
+      <c r="R2" s="2">
+        <v>4.1404007975570432E-5</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="40"/>
+      <c r="B3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="2">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E3" s="2">
+        <v>7.9320975394043007E-5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>9.5907997765742588E-4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3.7393014415337502E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1.2502379732506759E-5</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2.061262921650001E-12</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.5970269791634942E-11</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>6.3137151360857446E-10</v>
+      </c>
+      <c r="R3" s="2">
+        <v>5.5398775638762888E-5</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="40"/>
+      <c r="B4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="2">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="E4" s="2">
+        <v>9.0808819569714397E-5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1.1087769706778351E-3</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4.2800397009342978E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1.428430207773454E-5</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2.1310124551317748E-12</v>
+      </c>
+      <c r="L4" s="2">
+        <v>4.0113258772253033E-11</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>7.2214227504260378E-10</v>
+      </c>
+      <c r="R4" s="2">
+        <v>6.2857680525438069E-5</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="2">
+        <v>0.123</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.7000007305535739E-4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2.263437057505247E-10</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2.1300004392060569E-3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1.9450001005015451E-4</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1.7211294166641639E-19</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1.4704711801728749E-18</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>8.0000041227173491E-10</v>
+      </c>
+      <c r="R5" s="2">
+        <v>5.0000002618555569E-4</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="40"/>
+      <c r="B6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.7000007305535739E-4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4.234524080770903E-10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2.1300004392060569E-3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1.9450001005015451E-4</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1.777149347716957E-19</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1.4704711801728749E-18</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>8.0000041227173491E-10</v>
+      </c>
+      <c r="R6" s="2">
+        <v>5.0000002618555569E-4</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="40"/>
+      <c r="B7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3.7000007305535739E-4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6.5876736023791629E-10</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2.1300004392060569E-3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1.9450001005015451E-4</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1.8350337027916159E-19</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1.4704711801728749E-18</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>8.0000041227173491E-10</v>
+      </c>
+      <c r="R7" s="2">
+        <v>5.0000002618555569E-4</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="2">
+        <v>0.109</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.0635919449577962E-5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7.4095342276366287E-4</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2.8990310045492502E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.2766862972737553E-6</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>8.4634572408057941E-14</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2.079018417365221E-11</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>4.9862013029308978E-10</v>
+      </c>
+      <c r="R8" s="2">
+        <v>3.3699160048100651E-5</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="40"/>
+      <c r="B9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="32"/>
+      <c r="D9" s="2">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E9" s="2">
+        <v>8.479788055787028E-5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.0190034673629069E-3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>4.0542253951968528E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1.297322329497544E-5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1.0032609837261589E-13</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2.874483060369739E-11</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>6.9869409958394093E-10</v>
+      </c>
+      <c r="R9" s="2">
+        <v>4.7127456028240328E-5</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="40"/>
+      <c r="B10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="6">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="E10" s="6">
+        <v>9.0625197857766731E-5</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1.084765054437642E-3</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>4.3328320886398732E-4</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1.3864743961022141E-5</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1.0403330264304169E-13</v>
+      </c>
+      <c r="L10" s="2">
+        <v>3.0636883674030443E-11</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>7.4706451762208608E-10</v>
+      </c>
+      <c r="R10" s="6">
+        <v>5.036605233546229E-5</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="32"/>
+      <c r="D11" s="2">
+        <v>0.123</v>
+      </c>
+      <c r="E11" s="2">
+        <v>9.5925803079973514E-10</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1.472297681527875E-8</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4.6592218287943913E-9</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1.7462691676107691E-10</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1.567633484878281E-19</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1.686196742833066E-15</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>5.3277829996490928E-15</v>
+      </c>
+      <c r="R11" s="2">
+        <v>2.7932592101629562E-9</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="40"/>
+      <c r="B12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="E12" s="2">
+        <v>9.5925803079973514E-10</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.472297681527875E-8</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>4.6592218287943913E-9</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1.7462691676107691E-10</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1.567633484878281E-19</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1.686196742833066E-15</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>5.3277829996490928E-15</v>
+      </c>
+      <c r="R12" s="2">
+        <v>2.7932592101629562E-9</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="40"/>
+      <c r="B13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="32"/>
+      <c r="D14" s="8">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3.3666983701414268E-10</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1.0802794030402971E-9</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1.644587675689373E-9</v>
+      </c>
+      <c r="I14" s="8">
+        <v>6.5878592955688405E-11</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>2.8972773196526259E-19</v>
+      </c>
+      <c r="L14" s="8">
+        <v>7.2648121207230439E-19</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>1.825672920617115E-15</v>
+      </c>
+      <c r="R14" s="8">
+        <v>1.9166713129052312E-9</v>
+      </c>
+      <c r="S14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="40"/>
+      <c r="B15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="32"/>
+      <c r="D15" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6.1950677617101774E-10</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2.005665874784855E-9</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>3.0250338022389089E-9</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1.2079676202134451E-10</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2.9631200935494931E-19</v>
+      </c>
+      <c r="L15" s="2">
+        <v>9.3058409942292208E-19</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>3.361076919616526E-15</v>
+      </c>
+      <c r="R15" s="2">
+        <v>3.485007288992924E-9</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="40"/>
+      <c r="B16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="32"/>
+      <c r="D16" s="2">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="E16" s="2">
+        <v>7.9416252283447699E-10</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.6275596442281308E-9</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>3.8773757582945176E-9</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1.546822546895375E-10</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <v>2.9990103074194639E-19</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1.0637433849284071E-18</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>4.3078310615297009E-15</v>
+      </c>
+      <c r="R16" s="2">
+        <v>4.4515381590099068E-9</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2.4403150857629862E-5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2.9800846949522069E-4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1.151080217305094E-4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3.8704220070653284E-6</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <v>9.1850283195580356E-13</v>
+      </c>
+      <c r="L17" s="2">
+        <v>2.205477607886596E-11</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>1.9417781447004059E-10</v>
+      </c>
+      <c r="R17" s="2">
+        <v>1.8200866089679621E-5</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="42"/>
+      <c r="B18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="2">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2.7506937937215451E-5</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3.3717130058539012E-4</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1.296705660823636E-4</v>
+      </c>
+      <c r="I18" s="2">
+        <v>4.3352226524314363E-6</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>8.0147418425023589E-13</v>
+      </c>
+      <c r="L18" s="2">
+        <v>2.3840364111115271E-11</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>2.1885489826218371E-10</v>
+      </c>
+      <c r="R18" s="2">
+        <v>1.964233257300441E-5</v>
+      </c>
+      <c r="S18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="42"/>
+      <c r="B19" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2.417188337654076E-5</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2.9662363596676729E-4</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1.1393189387279701E-4</v>
+      </c>
+      <c r="I19" s="2">
+        <v>3.803644606630916E-6</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>6.5977225890643007E-13</v>
+      </c>
+      <c r="L19" s="2">
+        <v>2.0718612443857501E-11</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>1.9231837459599011E-10</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1.7071382644377551E-5</v>
+      </c>
+      <c r="S19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="42"/>
+      <c r="B20" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="2">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2.4403150857629862E-5</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2.9800846949522069E-4</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>1.151080217305094E-4</v>
+      </c>
+      <c r="I20" s="2">
+        <v>3.8704220070653284E-6</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>9.1850283195580356E-13</v>
+      </c>
+      <c r="L20" s="2">
+        <v>2.205477607886596E-11</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>1.9417781447004059E-10</v>
+      </c>
+      <c r="R20" s="2">
+        <v>1.8200866089679621E-5</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="42"/>
+      <c r="B21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="46"/>
+      <c r="D21" s="2">
+        <f>D18*3</f>
+        <v>7.8E-2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2.7506937937215451E-5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>3.3717130058539012E-4</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1.296705660823636E-4</v>
+      </c>
+      <c r="I21" s="2">
+        <v>4.3352226524314363E-6</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>8.0147418425023589E-13</v>
+      </c>
+      <c r="L21" s="2">
+        <v>2.3840364111115271E-11</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>2.1885489826218371E-10</v>
+      </c>
+      <c r="R21" s="2">
+        <v>1.964233257300441E-5</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="43"/>
+      <c r="B22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="2">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2.417188337654076E-5</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2.9662363596676729E-4</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1.1393189387279701E-4</v>
+      </c>
+      <c r="I22" s="2">
+        <v>3.803644606630916E-6</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>6.5977225890643007E-13</v>
+      </c>
+      <c r="L22" s="2">
+        <v>2.0718612443857501E-11</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>1.9231837459599011E-10</v>
+      </c>
+      <c r="R22" s="2">
+        <v>1.7071382644377551E-5</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="42"/>
+      <c r="B24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="46"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="42"/>
+      <c r="B25" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="42"/>
+      <c r="B26" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="45">
+        <v>2050</v>
+      </c>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" s="42"/>
+      <c r="B27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="46"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" s="43"/>
+      <c r="B28" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="40"/>
+      <c r="B30" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="46"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" s="40"/>
+      <c r="B31" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="47"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A32" s="40"/>
+      <c r="B32" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33"/>
+      <c r="S32" s="33"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="40"/>
+      <c r="B33" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="46"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="40"/>
+      <c r="B34" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="47"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E420AB55-EC4C-449A-867B-1D5EF323C674}">
   <dimension ref="A1:Q90"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4661,13 +6652,13 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>77</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="40" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="4"/>
@@ -4692,14 +6683,14 @@
       <c r="K2" s="2">
         <v>0</v>
       </c>
-      <c r="M2" s="33"/>
+      <c r="M2" s="30"/>
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38"/>
+      <c r="A3" s="40"/>
       <c r="B3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="38"/>
+      <c r="C3" s="40"/>
       <c r="D3" s="4"/>
       <c r="E3" s="2">
         <v>0</v>
@@ -4722,14 +6713,14 @@
       <c r="K3" s="2">
         <v>0</v>
       </c>
-      <c r="M3" s="33"/>
+      <c r="M3" s="30"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="38"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="38"/>
+      <c r="C4" s="40"/>
       <c r="D4" s="9"/>
       <c r="E4" s="2">
         <v>0</v>
@@ -4755,11 +6746,11 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="38"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="40" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="10"/>
@@ -4787,11 +6778,11 @@
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="38"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="10"/>
       <c r="E6" s="2">
         <v>0</v>
@@ -4817,11 +6808,11 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="38"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="10"/>
       <c r="E7" s="2">
         <v>0</v>
@@ -4847,11 +6838,11 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
+      <c r="A8" s="40"/>
       <c r="B8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="40" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="10"/>
@@ -4879,11 +6870,11 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="38"/>
+      <c r="C9" s="40"/>
       <c r="D9" s="10"/>
       <c r="E9" s="2">
         <v>0</v>
@@ -4909,11 +6900,11 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="38"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="10"/>
       <c r="E10" s="2">
         <v>0</v>
@@ -4939,11 +6930,11 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="38"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="40" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="10"/>
@@ -4971,11 +6962,11 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="38"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="10"/>
       <c r="E12" s="2">
         <v>0</v>
@@ -5001,11 +6992,11 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="38"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="10"/>
       <c r="E13" s="2">
         <v>0</v>
@@ -5031,11 +7022,11 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="40" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="10"/>
@@ -5063,11 +7054,11 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="38"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="38"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="10"/>
       <c r="E15" s="2">
         <v>0</v>
@@ -5093,11 +7084,11 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="38"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="38"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="10"/>
       <c r="E16" s="2">
         <v>0</v>
@@ -5123,14 +7114,14 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="45" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="2">
@@ -5157,12 +7148,12 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="40"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="46"/>
       <c r="E18" s="2">
         <v>0</v>
       </c>
@@ -5187,12 +7178,12 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="41"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="47"/>
       <c r="E19" s="2">
         <v>0</v>
       </c>
@@ -5217,12 +7208,12 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="38"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="39" t="s">
+      <c r="C20" s="42"/>
+      <c r="D20" s="45" t="s">
         <v>43</v>
       </c>
       <c r="E20" s="2">
@@ -5249,12 +7240,12 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="38"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="40"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="46"/>
       <c r="E21" s="2">
         <v>0</v>
       </c>
@@ -5279,12 +7270,12 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="38"/>
+      <c r="A22" s="40"/>
       <c r="B22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="41"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="47"/>
       <c r="E22" s="2">
         <v>0</v>
       </c>
@@ -5309,14 +7300,14 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
+      <c r="A23" s="40"/>
       <c r="B23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="D23" s="45" t="s">
         <v>72</v>
       </c>
       <c r="E23" s="2">
@@ -5343,12 +7334,12 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
+      <c r="A24" s="40"/>
       <c r="B24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="40"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="46"/>
       <c r="E24" s="2">
         <v>0</v>
       </c>
@@ -5373,12 +7364,12 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
+      <c r="A25" s="40"/>
       <c r="B25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="47"/>
       <c r="E25" s="2">
         <v>0</v>
       </c>
@@ -5403,12 +7394,12 @@
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+      <c r="A26" s="40"/>
       <c r="B26" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="36"/>
-      <c r="D26" s="39">
+      <c r="C26" s="42"/>
+      <c r="D26" s="45">
         <v>2050</v>
       </c>
       <c r="E26" s="2">
@@ -5435,12 +7426,12 @@
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="38"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="36"/>
-      <c r="D27" s="40"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="46"/>
       <c r="E27" s="2">
         <v>0</v>
       </c>
@@ -5465,12 +7456,12 @@
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="38"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="41"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="47"/>
       <c r="E28" s="2">
         <v>0</v>
       </c>
@@ -5495,14 +7486,14 @@
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="38"/>
+      <c r="A29" s="40"/>
       <c r="B29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="39" t="s">
+      <c r="D29" s="45" t="s">
         <v>41</v>
       </c>
       <c r="E29" s="2">
@@ -5529,12 +7520,12 @@
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+      <c r="A30" s="40"/>
       <c r="B30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="40"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="46"/>
       <c r="E30" s="2">
         <v>0</v>
       </c>
@@ -5559,12 +7550,12 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="38"/>
+      <c r="A31" s="40"/>
       <c r="B31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="36"/>
-      <c r="D31" s="41"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="47"/>
       <c r="E31" s="2">
         <v>0</v>
       </c>
@@ -5589,12 +7580,12 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="38"/>
+      <c r="A32" s="40"/>
       <c r="B32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="39" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="45" t="s">
         <v>42</v>
       </c>
       <c r="E32" s="2">
@@ -5621,12 +7612,12 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="38"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="40"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="46"/>
       <c r="E33" s="2">
         <v>0</v>
       </c>
@@ -5651,12 +7642,12 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="38"/>
+      <c r="A34" s="40"/>
       <c r="B34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="41"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="47"/>
       <c r="E34" s="2">
         <v>0</v>
       </c>
@@ -5735,10 +7726,10 @@
       <c r="F41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="H41" s="32"/>
+      <c r="H41" s="29"/>
       <c r="I41" s="1" t="s">
         <v>58</v>
       </c>
@@ -5789,11 +7780,11 @@
       <c r="M44" s="11"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="43"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="54"/>
       <c r="D45" s="4" t="s">
         <v>48</v>
       </c>
@@ -5803,7 +7794,7 @@
       <c r="F45" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="37" t="s">
         <v>92</v>
       </c>
       <c r="H45" s="4" t="s">
@@ -5812,10 +7803,10 @@
       <c r="I45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="47" t="s">
+      <c r="J45" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="K45" s="48"/>
+      <c r="K45" s="51"/>
       <c r="L45" s="4" t="s">
         <v>96</v>
       </c>
@@ -5825,16 +7816,16 @@
       <c r="P45" s="4"/>
     </row>
     <row r="46" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="44"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="45"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="55"/>
       <c r="D46" s="15" t="s">
         <v>108</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="F46" s="27" t="s">
+      <c r="F46" s="26" t="s">
         <v>110</v>
       </c>
       <c r="G46" s="17" t="s">
@@ -5846,23 +7837,23 @@
       <c r="I46" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="J46" s="49" t="s">
+      <c r="J46" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="K46" s="50"/>
+      <c r="K46" s="53"/>
       <c r="L46" s="14" t="s">
         <v>112</v>
       </c>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="38" t="s">
+      <c r="A47" s="40" t="s">
         <v>36</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C47" s="30"/>
+      <c r="C47" s="27"/>
       <c r="D47" s="2" t="s">
         <v>13</v>
       </c>
@@ -5872,6 +7863,9 @@
       <c r="F47" s="16" t="s">
         <v>6</v>
       </c>
+      <c r="G47" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H47" s="2">
         <v>0</v>
       </c>
@@ -5888,11 +7882,11 @@
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="40"/>
       <c r="B48" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="30"/>
+      <c r="C48" s="27"/>
       <c r="D48" s="2" t="s">
         <v>13</v>
       </c>
@@ -5902,7 +7896,9 @@
       <c r="F48" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="28"/>
+      <c r="G48" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H48" s="2">
         <v>0</v>
       </c>
@@ -5915,15 +7911,15 @@
       <c r="K48" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L48" s="25"/>
+      <c r="L48" s="24"/>
       <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="40"/>
       <c r="B49" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="30"/>
+      <c r="C49" s="27"/>
       <c r="D49" s="2" t="s">
         <v>13</v>
       </c>
@@ -5933,7 +7929,9 @@
       <c r="F49" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="28"/>
+      <c r="G49" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H49" s="2">
         <v>0</v>
       </c>
@@ -5946,17 +7944,17 @@
       <c r="K49" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L49" s="25"/>
+      <c r="L49" s="24"/>
       <c r="M49" s="11"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="38" t="s">
+      <c r="A50" s="40" t="s">
         <v>37</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="30"/>
+      <c r="C50" s="27"/>
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
@@ -5966,7 +7964,9 @@
       <c r="F50" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G50" s="28"/>
+      <c r="G50" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H50" s="2">
         <v>0</v>
       </c>
@@ -5979,15 +7979,15 @@
       <c r="K50" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L50" s="25"/>
+      <c r="L50" s="24"/>
       <c r="M50" s="11"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="40"/>
       <c r="B51" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="30"/>
+      <c r="C51" s="27"/>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
@@ -5997,7 +7997,9 @@
       <c r="F51" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G51" s="28"/>
+      <c r="G51" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H51" s="2">
         <v>0</v>
       </c>
@@ -6010,15 +8012,15 @@
       <c r="K51" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L51" s="25"/>
-      <c r="M51" s="42"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="48"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A52" s="38"/>
+      <c r="A52" s="40"/>
       <c r="B52" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="30"/>
+      <c r="C52" s="27"/>
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
@@ -6028,7 +8030,9 @@
       <c r="F52" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="28"/>
+      <c r="G52" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H52" s="2">
         <v>0</v>
       </c>
@@ -6041,17 +8045,17 @@
       <c r="K52" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L52" s="25"/>
-      <c r="M52" s="42"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="48"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A53" s="38" t="s">
+      <c r="A53" s="40" t="s">
         <v>38</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="30"/>
+      <c r="C53" s="27"/>
       <c r="D53" s="2" t="s">
         <v>13</v>
       </c>
@@ -6061,7 +8065,9 @@
       <c r="F53" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="28"/>
+      <c r="G53" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H53" s="2">
         <v>0</v>
       </c>
@@ -6074,15 +8080,15 @@
       <c r="K53" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L53" s="25"/>
-      <c r="M53" s="42"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="48"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" s="38"/>
+      <c r="A54" s="40"/>
       <c r="B54" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="30"/>
+      <c r="C54" s="27"/>
       <c r="D54" s="2" t="s">
         <v>13</v>
       </c>
@@ -6092,7 +8098,9 @@
       <c r="F54" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="28"/>
+      <c r="G54" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H54" s="2">
         <v>0</v>
       </c>
@@ -6105,15 +8113,15 @@
       <c r="K54" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L54" s="25"/>
-      <c r="M54" s="42"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="48"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" s="38"/>
+      <c r="A55" s="40"/>
       <c r="B55" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="30"/>
+      <c r="C55" s="27"/>
       <c r="D55" s="2" t="s">
         <v>13</v>
       </c>
@@ -6123,7 +8131,9 @@
       <c r="F55" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G55" s="28"/>
+      <c r="G55" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H55" s="2">
         <v>0</v>
       </c>
@@ -6136,17 +8146,17 @@
       <c r="K55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L55" s="25"/>
-      <c r="M55" s="42"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="48"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" s="38" t="s">
+      <c r="A56" s="40" t="s">
         <v>39</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C56" s="30"/>
+      <c r="C56" s="27"/>
       <c r="D56" s="2" t="s">
         <v>13</v>
       </c>
@@ -6156,7 +8166,9 @@
       <c r="F56" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G56" s="28"/>
+      <c r="G56" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H56" s="2">
         <v>0</v>
       </c>
@@ -6169,15 +8181,15 @@
       <c r="K56" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L56" s="25"/>
-      <c r="M56" s="42"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="48"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" s="38"/>
+      <c r="A57" s="40"/>
       <c r="B57" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C57" s="30"/>
+      <c r="C57" s="27"/>
       <c r="D57" s="2" t="s">
         <v>13</v>
       </c>
@@ -6187,7 +8199,9 @@
       <c r="F57" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="28"/>
+      <c r="G57" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H57" s="2">
         <v>0</v>
       </c>
@@ -6203,11 +8217,11 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" s="38"/>
+      <c r="A58" s="40"/>
       <c r="B58" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C58" s="30"/>
+      <c r="C58" s="27"/>
       <c r="D58" s="2" t="s">
         <v>13</v>
       </c>
@@ -6217,7 +8231,9 @@
       <c r="F58" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G58" s="28"/>
+      <c r="G58" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H58" s="2">
         <v>0</v>
       </c>
@@ -6233,13 +8249,13 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" s="38" t="s">
+      <c r="A59" s="40" t="s">
         <v>40</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="30"/>
+      <c r="C59" s="27"/>
       <c r="D59" s="2" t="s">
         <v>13</v>
       </c>
@@ -6249,7 +8265,9 @@
       <c r="F59" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="28"/>
+      <c r="G59" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H59" s="2">
         <v>0</v>
       </c>
@@ -6265,11 +8283,11 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A60" s="38"/>
+      <c r="A60" s="40"/>
       <c r="B60" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C60" s="30"/>
+      <c r="C60" s="27"/>
       <c r="D60" s="2" t="s">
         <v>13</v>
       </c>
@@ -6279,7 +8297,9 @@
       <c r="F60" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="28"/>
+      <c r="G60" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H60" s="2">
         <v>0</v>
       </c>
@@ -6295,11 +8315,11 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" s="38"/>
+      <c r="A61" s="40"/>
       <c r="B61" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C61" s="30"/>
+      <c r="C61" s="27"/>
       <c r="D61" s="2" t="s">
         <v>13</v>
       </c>
@@ -6309,7 +8329,9 @@
       <c r="F61" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="28"/>
+      <c r="G61" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H61" s="2">
         <v>0</v>
       </c>
@@ -6325,13 +8347,13 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="41" t="s">
         <v>70</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="39" t="s">
+      <c r="C62" s="45" t="s">
         <v>73</v>
       </c>
       <c r="D62" s="2" t="s">
@@ -6343,7 +8365,9 @@
       <c r="F62" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G62" s="29"/>
+      <c r="G62" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H62" s="2">
         <v>0</v>
       </c>
@@ -6359,11 +8383,11 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A63" s="36"/>
+      <c r="A63" s="42"/>
       <c r="B63" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="40"/>
+      <c r="C63" s="46"/>
       <c r="D63" s="2" t="s">
         <v>20</v>
       </c>
@@ -6373,7 +8397,9 @@
       <c r="F63" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G63" s="29"/>
+      <c r="G63" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H63" s="2">
         <v>0</v>
       </c>
@@ -6389,11 +8415,11 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A64" s="36"/>
+      <c r="A64" s="42"/>
       <c r="B64" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C64" s="41"/>
+      <c r="C64" s="47"/>
       <c r="D64" s="2" t="s">
         <v>20</v>
       </c>
@@ -6403,7 +8429,9 @@
       <c r="F64" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G64" s="29"/>
+      <c r="G64" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H64" s="2">
         <v>0</v>
       </c>
@@ -6419,11 +8447,11 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="36"/>
+      <c r="A65" s="42"/>
       <c r="B65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="45" t="s">
         <v>43</v>
       </c>
       <c r="D65" s="2" t="s">
@@ -6435,7 +8463,9 @@
       <c r="F65" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="G65" s="29"/>
+      <c r="G65" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H65" s="2">
         <v>0</v>
       </c>
@@ -6451,11 +8481,11 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="36"/>
+      <c r="A66" s="42"/>
       <c r="B66" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C66" s="40"/>
+      <c r="C66" s="46"/>
       <c r="D66" s="2" t="s">
         <v>20</v>
       </c>
@@ -6465,7 +8495,9 @@
       <c r="F66" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="29"/>
+      <c r="G66" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H66" s="2">
         <v>0</v>
       </c>
@@ -6481,11 +8513,11 @@
       <c r="L66" s="2"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
+      <c r="A67" s="43"/>
       <c r="B67" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="41"/>
+      <c r="C67" s="47"/>
       <c r="D67" s="2" t="s">
         <v>20</v>
       </c>
@@ -6495,7 +8527,9 @@
       <c r="F67" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="G67" s="29"/>
+      <c r="G67" s="38" t="s">
+        <v>122</v>
+      </c>
       <c r="H67" s="2">
         <v>0</v>
       </c>
@@ -6511,13 +8545,13 @@
       <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="35" t="s">
+      <c r="A68" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="39" t="s">
+      <c r="C68" s="45" t="s">
         <v>72</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -6526,10 +8560,12 @@
       <c r="E68" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F68" s="25" t="s">
+      <c r="F68" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="G68" s="29"/>
+      <c r="G68" s="38" t="s">
+        <v>123</v>
+      </c>
       <c r="H68" s="2">
         <v>0</v>
       </c>
@@ -6545,21 +8581,23 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="36"/>
+      <c r="A69" s="42"/>
       <c r="B69" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="40"/>
+      <c r="C69" s="46"/>
       <c r="D69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="25" t="s">
+      <c r="F69" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="G69" s="29"/>
+      <c r="G69" s="38" t="s">
+        <v>123</v>
+      </c>
       <c r="H69" s="2">
         <v>0</v>
       </c>
@@ -6575,21 +8613,23 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="36"/>
+      <c r="A70" s="42"/>
       <c r="B70" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C70" s="41"/>
+      <c r="C70" s="47"/>
       <c r="D70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F70" s="25" t="s">
+      <c r="F70" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="G70" s="29"/>
+      <c r="G70" s="38" t="s">
+        <v>123</v>
+      </c>
       <c r="H70" s="2">
         <v>0</v>
       </c>
@@ -6605,11 +8645,11 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
+      <c r="A71" s="42"/>
       <c r="B71" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C71" s="39">
+      <c r="C71" s="45">
         <v>2050</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -6618,10 +8658,12 @@
       <c r="E71" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F71" s="25" t="s">
+      <c r="F71" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="G71" s="29"/>
+      <c r="G71" s="38" t="s">
+        <v>123</v>
+      </c>
       <c r="H71" s="2">
         <v>0</v>
       </c>
@@ -6637,21 +8679,23 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
+      <c r="A72" s="42"/>
       <c r="B72" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="40"/>
+      <c r="C72" s="46"/>
       <c r="D72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="25" t="s">
+      <c r="F72" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="G72" s="29"/>
+      <c r="G72" s="38" t="s">
+        <v>123</v>
+      </c>
       <c r="H72" s="2">
         <v>0</v>
       </c>
@@ -6667,21 +8711,23 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
+      <c r="A73" s="43"/>
       <c r="B73" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="41"/>
+      <c r="C73" s="47"/>
       <c r="D73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="25" t="s">
+      <c r="F73" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="G73" s="29"/>
+      <c r="G73" s="38" t="s">
+        <v>123</v>
+      </c>
       <c r="H73" s="2">
         <v>0</v>
       </c>
@@ -6697,26 +8743,28 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="38" t="s">
+      <c r="A74" s="40" t="s">
         <v>44</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="39" t="s">
+      <c r="C74" s="45" t="s">
         <v>41</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E74" s="25">
-        <v>0</v>
-      </c>
-      <c r="F74" s="25" t="s">
+      <c r="E74" s="24">
+        <v>0</v>
+      </c>
+      <c r="F74" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G74" s="29"/>
-      <c r="H74" s="25" t="s">
+      <c r="G74" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H74" s="24" t="s">
         <v>113</v>
       </c>
       <c r="I74" s="4" t="s">
@@ -6731,22 +8779,24 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="38"/>
+      <c r="A75" s="40"/>
       <c r="B75" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="40"/>
+      <c r="C75" s="46"/>
       <c r="D75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E75" s="25">
-        <v>0</v>
-      </c>
-      <c r="F75" s="25" t="s">
+      <c r="E75" s="24">
+        <v>0</v>
+      </c>
+      <c r="F75" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G75" s="29"/>
-      <c r="H75" s="25" t="s">
+      <c r="G75" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H75" s="24" t="s">
         <v>113</v>
       </c>
       <c r="I75" s="4" t="s">
@@ -6761,22 +8811,24 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="38"/>
+      <c r="A76" s="40"/>
       <c r="B76" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="41"/>
+      <c r="C76" s="47"/>
       <c r="D76" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E76" s="25">
-        <v>0</v>
-      </c>
-      <c r="F76" s="25" t="s">
+      <c r="E76" s="24">
+        <v>0</v>
+      </c>
+      <c r="F76" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G76" s="29"/>
-      <c r="H76" s="25" t="s">
+      <c r="G76" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H76" s="24" t="s">
         <v>113</v>
       </c>
       <c r="I76" s="4" t="s">
@@ -6791,24 +8843,26 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="38"/>
+      <c r="A77" s="40"/>
       <c r="B77" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C77" s="39" t="s">
+      <c r="C77" s="45" t="s">
         <v>42</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E77" s="25">
-        <v>0</v>
-      </c>
-      <c r="F77" s="25" t="s">
+      <c r="E77" s="24">
+        <v>0</v>
+      </c>
+      <c r="F77" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G77" s="29"/>
-      <c r="H77" s="25" t="s">
+      <c r="G77" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H77" s="24" t="s">
         <v>113</v>
       </c>
       <c r="I77" s="4" t="s">
@@ -6823,22 +8877,24 @@
       <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="38"/>
+      <c r="A78" s="40"/>
       <c r="B78" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="40"/>
+      <c r="C78" s="46"/>
       <c r="D78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E78" s="25">
-        <v>0</v>
-      </c>
-      <c r="F78" s="25" t="s">
+      <c r="E78" s="24">
+        <v>0</v>
+      </c>
+      <c r="F78" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G78" s="29"/>
-      <c r="H78" s="25" t="s">
+      <c r="G78" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H78" s="24" t="s">
         <v>113</v>
       </c>
       <c r="I78" s="4" t="s">
@@ -6853,22 +8909,24 @@
       <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="38"/>
+      <c r="A79" s="40"/>
       <c r="B79" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C79" s="41"/>
+      <c r="C79" s="47"/>
       <c r="D79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E79" s="25">
-        <v>0</v>
-      </c>
-      <c r="F79" s="25" t="s">
+      <c r="E79" s="24">
+        <v>0</v>
+      </c>
+      <c r="F79" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25" t="s">
+      <c r="G79" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H79" s="24" t="s">
         <v>113</v>
       </c>
       <c r="I79" s="4" t="s">
@@ -6883,54 +8941,69 @@
       <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E80" s="23"/>
-      <c r="F80" s="26"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="25"/>
     </row>
     <row r="81" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E81" s="23"/>
-      <c r="F81" s="26"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="25"/>
     </row>
     <row r="82" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E82" s="23"/>
-      <c r="F82" s="26"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="25"/>
     </row>
     <row r="83" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E83" s="23"/>
-      <c r="F83" s="26"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="25"/>
     </row>
     <row r="84" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E84" s="24"/>
-      <c r="F84" s="26"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="25"/>
     </row>
     <row r="85" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E85" s="46"/>
-      <c r="F85" s="26"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="25"/>
     </row>
     <row r="86" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E86" s="43"/>
-      <c r="F86" s="26"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="25"/>
     </row>
     <row r="87" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E87" s="43"/>
-      <c r="F87" s="26"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="25"/>
     </row>
     <row r="88" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E88" s="43"/>
-      <c r="F88" s="26"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="25"/>
     </row>
     <row r="89" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E89" s="43"/>
-      <c r="F89" s="26"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="25"/>
     </row>
     <row r="90" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E90" s="45"/>
+      <c r="E90" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C77:C79"/>
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="A2:A34"/>
     <mergeCell ref="M51:M53"/>
+    <mergeCell ref="E85:E90"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A68:A73"/>
+    <mergeCell ref="A74:A79"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="C68:C70"/>
     <mergeCell ref="M54:M56"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C5:C7"/>
@@ -6946,86 +9019,355 @@
     <mergeCell ref="J45:K45"/>
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="C29:C34"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C77:C79"/>
     <mergeCell ref="A45:C46"/>
-    <mergeCell ref="E85:E90"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A67"/>
-    <mergeCell ref="A68:A73"/>
-    <mergeCell ref="A74:A79"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="C71:C73"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3ACA8CF-C794-4F64-B8FF-076CB5E79407}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB363C3-7514-4141-8E82-8E2B2A7D183A}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C67"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="251.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>100</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C13" s="39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="42"/>
+      <c r="B15" s="40"/>
+      <c r="C15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="42"/>
+      <c r="B16" s="40"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="42"/>
+      <c r="B17" s="40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="42"/>
+      <c r="B18" s="40"/>
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="43"/>
+      <c r="B19" s="40"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="42"/>
+      <c r="B21" s="44"/>
+      <c r="C21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="42"/>
+      <c r="B22" s="44"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="42"/>
+      <c r="B23" s="40">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="42"/>
+      <c r="B24" s="40"/>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="43"/>
+      <c r="B25" s="40"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="40"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="40"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="20"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="40"/>
+      <c r="B29" s="40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="40"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="40"/>
+      <c r="B31" s="40"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="40" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="40"/>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="40"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="40"/>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="40"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="40"/>
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="40"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="40"/>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="40"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="40"/>
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="40"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="41" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="42"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="42"/>
+      <c r="B52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="42"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="42"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="43"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="42"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="42"/>
+      <c r="B58" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="42"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="42"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="43"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="42"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="42"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="42"/>
+      <c r="B65" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="42"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="43"/>
+    </row>
   </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="232e48a4-996a-4688-951c-c513fbc1255c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="054690b1-a5d8-490b-abb5-be9830757502">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="054690b1-a5d8-490b-abb5-be9830757502" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7296,21 +9638,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="232e48a4-996a-4688-951c-c513fbc1255c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="054690b1-a5d8-490b-abb5-be9830757502">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="054690b1-a5d8-490b-abb5-be9830757502" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688F3E42-A9A9-4B55-809D-F423D84F64A1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15A8345F-B5BB-4013-8234-B3F44FED454D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="232e48a4-996a-4688-951c-c513fbc1255c"/>
-    <ds:schemaRef ds:uri="054690b1-a5d8-490b-abb5-be9830757502"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7335,9 +9677,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15A8345F-B5BB-4013-8234-B3F44FED454D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688F3E42-A9A9-4B55-809D-F423D84F64A1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="232e48a4-996a-4688-951c-c513fbc1255c"/>
+    <ds:schemaRef ds:uri="054690b1-a5d8-490b-abb5-be9830757502"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/lca_database.xlsx
+++ b/data/lca_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DERLL\Documents\MA1\Q2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F34FDBF-D05A-481C-B4DF-3954796C131E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5058F9-8068-4137-9345-087CBD222796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Emission factor" sheetId="1" r:id="rId1"/>
@@ -708,7 +708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -793,9 +793,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -805,8 +802,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -817,10 +814,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -835,15 +841,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3355,11 +3356,11 @@
       <c r="Q20" s="2">
         <v>0</v>
       </c>
-      <c r="R20" s="2">
-        <v>0</v>
-      </c>
-      <c r="S20" s="2">
-        <v>0</v>
+      <c r="R20" s="57">
+        <v>-1.256627216299778E-4</v>
+      </c>
+      <c r="S20" s="57">
+        <v>-2.8871599981749041E-3</v>
       </c>
       <c r="T20" s="2">
         <v>-1.256627216299778E-4</v>
@@ -3423,11 +3424,11 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-      <c r="R21" s="2">
-        <v>0</v>
-      </c>
-      <c r="S21" s="2">
-        <v>0</v>
+      <c r="R21" s="57">
+        <v>-1.3054947063404359E-5</v>
+      </c>
+      <c r="S21" s="57">
+        <v>-3.9657900798125562E-5</v>
       </c>
       <c r="T21" s="2">
         <v>-1.3054947063404359E-5</v>
@@ -3531,17 +3532,17 @@
       <c r="A2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="43" t="s">
         <v>127</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="40">
         <v>200000</v>
       </c>
-      <c r="F2" s="41">
+      <c r="F2" s="40">
         <v>260000</v>
       </c>
       <c r="G2">
@@ -3584,11 +3585,11 @@
       <c r="A3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="40"/>
+      <c r="B3" s="43"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="2">
         <v>1552</v>
       </c>
@@ -3628,11 +3629,11 @@
       <c r="A4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="40"/>
+      <c r="B4" s="43"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
       <c r="G4" s="2">
         <v>1876</v>
       </c>
@@ -3672,13 +3673,13 @@
       <c r="A5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="43" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
       <c r="G5" s="7">
         <v>1270</v>
       </c>
@@ -3719,11 +3720,11 @@
       <c r="A6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="40"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="2">
         <v>1583</v>
       </c>
@@ -3763,11 +3764,11 @@
       <c r="A7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="40"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
       <c r="G7" s="2">
         <v>1828</v>
       </c>
@@ -3807,13 +3808,13 @@
       <c r="A8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="43" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
       <c r="G8" s="2">
         <v>1256</v>
       </c>
@@ -3853,11 +3854,11 @@
       <c r="A9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="40"/>
+      <c r="B9" s="43"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
       <c r="G9" s="2">
         <v>1434</v>
       </c>
@@ -3897,11 +3898,11 @@
       <c r="A10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="40"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
       <c r="G10" s="2">
         <v>1515</v>
       </c>
@@ -3941,13 +3942,13 @@
       <c r="A11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="43" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
       <c r="G11" s="2">
         <v>1165</v>
       </c>
@@ -3986,11 +3987,11 @@
       <c r="A12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="40"/>
+      <c r="B12" s="43"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
       <c r="G12" s="2">
         <v>1503</v>
       </c>
@@ -4029,11 +4030,11 @@
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="40"/>
+      <c r="B13" s="43"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
       <c r="G13" s="2">
         <v>0</v>
       </c>
@@ -4072,13 +4073,13 @@
       <c r="A14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="43" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
       <c r="G14" s="7">
         <v>1233</v>
       </c>
@@ -4118,11 +4119,11 @@
       <c r="A15" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="40"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
       <c r="G15" s="2">
         <v>1530</v>
       </c>
@@ -4163,11 +4164,11 @@
       <c r="A16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="40"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
       <c r="G16" s="2">
         <v>2197</v>
       </c>
@@ -4207,15 +4208,15 @@
       <c r="A17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
       <c r="G17" s="2">
         <v>1678</v>
       </c>
@@ -4256,11 +4257,11 @@
       <c r="A18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="2">
         <v>1880</v>
       </c>
@@ -4301,11 +4302,11 @@
       <c r="A19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
       <c r="G19" s="2">
         <v>2234</v>
       </c>
@@ -4345,13 +4346,13 @@
       <c r="A20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="41" t="s">
+      <c r="B20" s="41"/>
+      <c r="C20" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
       <c r="G20" s="2">
         <v>1678</v>
       </c>
@@ -4392,11 +4393,11 @@
       <c r="A21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
       <c r="G21" s="2">
         <v>1880</v>
       </c>
@@ -4437,11 +4438,11 @@
       <c r="A22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
       <c r="G22" s="2">
         <v>2234</v>
       </c>
@@ -4481,15 +4482,15 @@
       <c r="A23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="7">
         <v>1528</v>
       </c>
@@ -4528,11 +4529,11 @@
       <c r="A24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="2">
         <v>2025</v>
       </c>
@@ -4572,11 +4573,11 @@
       <c r="A25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="2">
         <v>2469</v>
       </c>
@@ -4615,13 +4616,13 @@
       <c r="A26" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="41">
+      <c r="B26" s="41"/>
+      <c r="C26" s="40">
         <v>2050</v>
       </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="7">
         <v>1528</v>
       </c>
@@ -4661,11 +4662,11 @@
       <c r="A27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="2">
         <v>2025</v>
       </c>
@@ -4706,11 +4707,11 @@
       <c r="A28" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
       <c r="G28" s="2">
         <v>2469</v>
       </c>
@@ -4750,15 +4751,15 @@
       <c r="A29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
       <c r="G29" s="7">
         <v>0</v>
       </c>
@@ -4798,11 +4799,11 @@
       <c r="A30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
       <c r="G30" s="2">
         <v>1800</v>
       </c>
@@ -4843,11 +4844,11 @@
       <c r="A31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
       <c r="G31" s="2">
         <v>0</v>
       </c>
@@ -4887,13 +4888,13 @@
       <c r="A32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="41" t="s">
+      <c r="B32" s="41"/>
+      <c r="C32" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
       <c r="G32" s="7">
         <v>0</v>
       </c>
@@ -4933,11 +4934,11 @@
       <c r="A33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="42"/>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
       <c r="G33" s="2">
         <v>1800</v>
       </c>
@@ -4978,11 +4979,11 @@
       <c r="A34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
       <c r="G34" s="2">
         <v>0</v>
       </c>
@@ -5072,14 +5073,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B17:B22"/>
-    <mergeCell ref="B29:B34"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
     <mergeCell ref="E2:E34"/>
     <mergeCell ref="F2:F34"/>
     <mergeCell ref="D2:D34"/>
@@ -5089,6 +5082,14 @@
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="C23:C25"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5100,9 +5101,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
+      <c r="A1" s="47"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
       <c r="D1" s="21" t="s">
         <v>77</v>
       </c>
@@ -5153,7 +5154,7 @@
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -5210,7 +5211,7 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="40"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="2" t="s">
         <v>69</v>
       </c>
@@ -5265,7 +5266,7 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="40"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="2" t="s">
         <v>68</v>
       </c>
@@ -5320,7 +5321,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="43" t="s">
         <v>37</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -5377,7 +5378,7 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="40"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="7" t="s">
         <v>69</v>
       </c>
@@ -5432,7 +5433,7 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="8" t="s">
         <v>68</v>
       </c>
@@ -5487,7 +5488,7 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="43" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -5544,7 +5545,7 @@
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="7" t="s">
         <v>69</v>
       </c>
@@ -5599,7 +5600,7 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="40"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="8" t="s">
         <v>68</v>
       </c>
@@ -5654,7 +5655,7 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="43" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -5711,7 +5712,7 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="40"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="7" t="s">
         <v>69</v>
       </c>
@@ -5766,7 +5767,7 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="40"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="8" t="s">
         <v>68</v>
       </c>
@@ -5789,7 +5790,7 @@
       <c r="S13" s="2"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -5846,7 +5847,7 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="7" t="s">
         <v>69</v>
       </c>
@@ -5901,7 +5902,7 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="40"/>
+      <c r="A16" s="43"/>
       <c r="B16" s="8" t="s">
         <v>68</v>
       </c>
@@ -5956,13 +5957,13 @@
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="40" t="s">
         <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="44" t="s">
         <v>73</v>
       </c>
       <c r="D17" s="2">
@@ -6015,11 +6016,11 @@
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="46"/>
+      <c r="C18" s="45"/>
       <c r="D18" s="2">
         <v>2.5999999999999999E-2</v>
       </c>
@@ -6070,11 +6071,11 @@
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="42"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="2">
         <v>2.8000000000000001E-2</v>
       </c>
@@ -6125,11 +6126,11 @@
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="42"/>
+      <c r="A20" s="41"/>
       <c r="B20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="44" t="s">
         <v>43</v>
       </c>
       <c r="D20" s="2">
@@ -6182,11 +6183,11 @@
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="42"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="46"/>
+      <c r="C21" s="45"/>
       <c r="D21" s="2">
         <f>D18*3</f>
         <v>7.8E-2</v>
@@ -6238,11 +6239,11 @@
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="43"/>
+      <c r="A22" s="42"/>
       <c r="B22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="47"/>
+      <c r="C22" s="46"/>
       <c r="D22" s="2">
         <v>8.4000000000000005E-2</v>
       </c>
@@ -6293,13 +6294,13 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="40" t="s">
         <v>71</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="44" t="s">
         <v>72</v>
       </c>
       <c r="D23" s="33"/>
@@ -6320,11 +6321,11 @@
       <c r="S23" s="33"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="42"/>
+      <c r="A24" s="41"/>
       <c r="B24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="46"/>
+      <c r="C24" s="45"/>
       <c r="D24" s="33"/>
       <c r="E24" s="33"/>
       <c r="F24" s="33"/>
@@ -6343,11 +6344,11 @@
       <c r="S24" s="33"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A25" s="42"/>
+      <c r="A25" s="41"/>
       <c r="B25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="47"/>
+      <c r="C25" s="46"/>
       <c r="D25" s="33"/>
       <c r="E25" s="33"/>
       <c r="F25" s="33"/>
@@ -6366,11 +6367,11 @@
       <c r="S25" s="33"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A26" s="42"/>
+      <c r="A26" s="41"/>
       <c r="B26" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="45">
+      <c r="C26" s="44">
         <v>2050</v>
       </c>
       <c r="D26" s="33"/>
@@ -6391,11 +6392,11 @@
       <c r="S26" s="33"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" s="42"/>
+      <c r="A27" s="41"/>
       <c r="B27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="46"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="33"/>
       <c r="E27" s="33"/>
       <c r="F27" s="33"/>
@@ -6414,11 +6415,11 @@
       <c r="S27" s="33"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A28" s="43"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="47"/>
+      <c r="C28" s="46"/>
       <c r="D28" s="33"/>
       <c r="E28" s="33"/>
       <c r="F28" s="33"/>
@@ -6437,13 +6438,13 @@
       <c r="S28" s="33"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="43" t="s">
         <v>44</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="44" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="33"/>
@@ -6464,11 +6465,11 @@
       <c r="S29" s="33"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
+      <c r="A30" s="43"/>
       <c r="B30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="46"/>
+      <c r="C30" s="45"/>
       <c r="D30" s="33"/>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
@@ -6487,11 +6488,11 @@
       <c r="S30" s="33"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+      <c r="A31" s="43"/>
       <c r="B31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="47"/>
+      <c r="C31" s="46"/>
       <c r="D31" s="33"/>
       <c r="E31" s="33"/>
       <c r="F31" s="33"/>
@@ -6510,11 +6511,11 @@
       <c r="S31" s="33"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
+      <c r="A32" s="43"/>
       <c r="B32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C32" s="44" t="s">
         <v>42</v>
       </c>
       <c r="D32" s="33"/>
@@ -6535,11 +6536,11 @@
       <c r="S32" s="33"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="46"/>
+      <c r="C33" s="45"/>
       <c r="D33" s="33"/>
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
@@ -6558,11 +6559,11 @@
       <c r="S33" s="33"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A34" s="40"/>
+      <c r="A34" s="43"/>
       <c r="B34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="47"/>
+      <c r="C34" s="46"/>
       <c r="D34" s="33"/>
       <c r="E34" s="33"/>
       <c r="F34" s="33"/>
@@ -6582,6 +6583,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="C32:C34"/>
@@ -6592,11 +6598,6 @@
     <mergeCell ref="A23:A28"/>
     <mergeCell ref="C23:C25"/>
     <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6652,13 +6653,13 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="43" t="s">
         <v>77</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="43" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="4"/>
@@ -6686,11 +6687,11 @@
       <c r="M2" s="30"/>
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="40"/>
+      <c r="C3" s="43"/>
       <c r="D3" s="4"/>
       <c r="E3" s="2">
         <v>0</v>
@@ -6716,11 +6717,11 @@
       <c r="M3" s="30"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="40"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="40"/>
+      <c r="C4" s="43"/>
       <c r="D4" s="9"/>
       <c r="E4" s="2">
         <v>0</v>
@@ -6746,11 +6747,11 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="40"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="43" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="10"/>
@@ -6778,11 +6779,11 @@
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="40"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="40"/>
+      <c r="C6" s="43"/>
       <c r="D6" s="10"/>
       <c r="E6" s="2">
         <v>0</v>
@@ -6808,11 +6809,11 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="40"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="43"/>
       <c r="D7" s="10"/>
       <c r="E7" s="2">
         <v>0</v>
@@ -6838,11 +6839,11 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="40"/>
+      <c r="A8" s="43"/>
       <c r="B8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="43" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="10"/>
@@ -6870,11 +6871,11 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="40"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="10"/>
       <c r="E9" s="2">
         <v>0</v>
@@ -6900,11 +6901,11 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="40"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="40"/>
+      <c r="C10" s="43"/>
       <c r="D10" s="10"/>
       <c r="E10" s="2">
         <v>0</v>
@@ -6930,11 +6931,11 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
+      <c r="A11" s="43"/>
       <c r="B11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="43" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="10"/>
@@ -6962,11 +6963,11 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="40"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="40"/>
+      <c r="C12" s="43"/>
       <c r="D12" s="10"/>
       <c r="E12" s="2">
         <v>0</v>
@@ -6992,11 +6993,11 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="40"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="40"/>
+      <c r="C13" s="43"/>
       <c r="D13" s="10"/>
       <c r="E13" s="2">
         <v>0</v>
@@ -7022,11 +7023,11 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="40"/>
+      <c r="A14" s="43"/>
       <c r="B14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="43" t="s">
         <v>40</v>
       </c>
       <c r="D14" s="10"/>
@@ -7054,11 +7055,11 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="40"/>
+      <c r="C15" s="43"/>
       <c r="D15" s="10"/>
       <c r="E15" s="2">
         <v>0</v>
@@ -7084,11 +7085,11 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="40"/>
+      <c r="A16" s="43"/>
       <c r="B16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="40"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="10"/>
       <c r="E16" s="2">
         <v>0</v>
@@ -7114,14 +7115,14 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="44" t="s">
         <v>73</v>
       </c>
       <c r="E17" s="2">
@@ -7148,12 +7149,12 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="46"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="45"/>
       <c r="E18" s="2">
         <v>0</v>
       </c>
@@ -7178,12 +7179,12 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
+      <c r="A19" s="43"/>
       <c r="B19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="47"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="2">
         <v>0</v>
       </c>
@@ -7208,12 +7209,12 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
+      <c r="A20" s="43"/>
       <c r="B20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="45" t="s">
+      <c r="C20" s="41"/>
+      <c r="D20" s="44" t="s">
         <v>43</v>
       </c>
       <c r="E20" s="2">
@@ -7240,12 +7241,12 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="46"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="45"/>
       <c r="E21" s="2">
         <v>0</v>
       </c>
@@ -7270,12 +7271,12 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="40"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="47"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="46"/>
       <c r="E22" s="2">
         <v>0</v>
       </c>
@@ -7300,14 +7301,14 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="40"/>
+      <c r="A23" s="43"/>
       <c r="B23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="44" t="s">
         <v>72</v>
       </c>
       <c r="E23" s="2">
@@ -7334,12 +7335,12 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="40"/>
+      <c r="A24" s="43"/>
       <c r="B24" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="46"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="45"/>
       <c r="E24" s="2">
         <v>0</v>
       </c>
@@ -7364,12 +7365,12 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="40"/>
+      <c r="A25" s="43"/>
       <c r="B25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="42"/>
-      <c r="D25" s="47"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="46"/>
       <c r="E25" s="2">
         <v>0</v>
       </c>
@@ -7394,12 +7395,12 @@
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
+      <c r="A26" s="43"/>
       <c r="B26" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="45">
+      <c r="C26" s="41"/>
+      <c r="D26" s="44">
         <v>2050</v>
       </c>
       <c r="E26" s="2">
@@ -7426,12 +7427,12 @@
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+      <c r="A27" s="43"/>
       <c r="B27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="46"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="45"/>
       <c r="E27" s="2">
         <v>0</v>
       </c>
@@ -7456,12 +7457,12 @@
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="40"/>
+      <c r="A28" s="43"/>
       <c r="B28" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="43"/>
-      <c r="D28" s="47"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="46"/>
       <c r="E28" s="2">
         <v>0</v>
       </c>
@@ -7486,14 +7487,14 @@
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
+      <c r="A29" s="43"/>
       <c r="B29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="44" t="s">
         <v>41</v>
       </c>
       <c r="E29" s="2">
@@ -7520,12 +7521,12 @@
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
+      <c r="A30" s="43"/>
       <c r="B30" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="46"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="45"/>
       <c r="E30" s="2">
         <v>0</v>
       </c>
@@ -7550,12 +7551,12 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
+      <c r="A31" s="43"/>
       <c r="B31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="47"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="46"/>
       <c r="E31" s="2">
         <v>0</v>
       </c>
@@ -7580,12 +7581,12 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="40"/>
+      <c r="A32" s="43"/>
       <c r="B32" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="45" t="s">
+      <c r="C32" s="41"/>
+      <c r="D32" s="44" t="s">
         <v>42</v>
       </c>
       <c r="E32" s="2">
@@ -7612,12 +7613,12 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="46"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="45"/>
       <c r="E33" s="2">
         <v>0</v>
       </c>
@@ -7642,12 +7643,12 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="40"/>
+      <c r="A34" s="43"/>
       <c r="B34" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="47"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="46"/>
       <c r="E34" s="2">
         <v>0</v>
       </c>
@@ -7784,7 +7785,7 @@
         <v>115</v>
       </c>
       <c r="B45" s="48"/>
-      <c r="C45" s="54"/>
+      <c r="C45" s="50"/>
       <c r="D45" s="4" t="s">
         <v>48</v>
       </c>
@@ -7803,10 +7804,10 @@
       <c r="I45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="50" t="s">
+      <c r="J45" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="K45" s="51"/>
+      <c r="K45" s="53"/>
       <c r="L45" s="4" t="s">
         <v>96</v>
       </c>
@@ -7816,9 +7817,9 @@
       <c r="P45" s="4"/>
     </row>
     <row r="46" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="49"/>
-      <c r="B46" s="49"/>
-      <c r="C46" s="55"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="51"/>
       <c r="D46" s="15" t="s">
         <v>108</v>
       </c>
@@ -7837,17 +7838,17 @@
       <c r="I46" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="J46" s="52" t="s">
+      <c r="J46" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="K46" s="53"/>
+      <c r="K46" s="55"/>
       <c r="L46" s="14" t="s">
         <v>112</v>
       </c>
       <c r="M46" s="11"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -7882,7 +7883,7 @@
       <c r="M47" s="11"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="40"/>
+      <c r="A48" s="43"/>
       <c r="B48" s="2" t="s">
         <v>69</v>
       </c>
@@ -7915,7 +7916,7 @@
       <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
+      <c r="A49" s="43"/>
       <c r="B49" s="8" t="s">
         <v>68</v>
       </c>
@@ -7948,7 +7949,7 @@
       <c r="M49" s="11"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="40" t="s">
+      <c r="A50" s="43" t="s">
         <v>37</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -7983,7 +7984,7 @@
       <c r="M50" s="11"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+      <c r="A51" s="43"/>
       <c r="B51" s="7" t="s">
         <v>69</v>
       </c>
@@ -8016,7 +8017,7 @@
       <c r="M51" s="48"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A52" s="40"/>
+      <c r="A52" s="43"/>
       <c r="B52" s="8" t="s">
         <v>68</v>
       </c>
@@ -8049,7 +8050,7 @@
       <c r="M52" s="48"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A53" s="40" t="s">
+      <c r="A53" s="43" t="s">
         <v>38</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -8084,7 +8085,7 @@
       <c r="M53" s="48"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A54" s="40"/>
+      <c r="A54" s="43"/>
       <c r="B54" s="7" t="s">
         <v>69</v>
       </c>
@@ -8117,7 +8118,7 @@
       <c r="M54" s="48"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A55" s="40"/>
+      <c r="A55" s="43"/>
       <c r="B55" s="8" t="s">
         <v>68</v>
       </c>
@@ -8150,7 +8151,7 @@
       <c r="M55" s="48"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="43" t="s">
         <v>39</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -8185,7 +8186,7 @@
       <c r="M56" s="48"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" s="40"/>
+      <c r="A57" s="43"/>
       <c r="B57" s="7" t="s">
         <v>69</v>
       </c>
@@ -8217,7 +8218,7 @@
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" s="40"/>
+      <c r="A58" s="43"/>
       <c r="B58" s="8" t="s">
         <v>68</v>
       </c>
@@ -8249,7 +8250,7 @@
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" s="40" t="s">
+      <c r="A59" s="43" t="s">
         <v>40</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -8283,7 +8284,7 @@
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A60" s="40"/>
+      <c r="A60" s="43"/>
       <c r="B60" s="7" t="s">
         <v>69</v>
       </c>
@@ -8315,7 +8316,7 @@
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" s="40"/>
+      <c r="A61" s="43"/>
       <c r="B61" s="8" t="s">
         <v>68</v>
       </c>
@@ -8347,13 +8348,13 @@
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A62" s="41" t="s">
+      <c r="A62" s="40" t="s">
         <v>70</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="45" t="s">
+      <c r="C62" s="44" t="s">
         <v>73</v>
       </c>
       <c r="D62" s="2" t="s">
@@ -8383,11 +8384,11 @@
       <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A63" s="42"/>
+      <c r="A63" s="41"/>
       <c r="B63" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="46"/>
+      <c r="C63" s="45"/>
       <c r="D63" s="2" t="s">
         <v>20</v>
       </c>
@@ -8415,11 +8416,11 @@
       <c r="L63" s="2"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A64" s="42"/>
+      <c r="A64" s="41"/>
       <c r="B64" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C64" s="47"/>
+      <c r="C64" s="46"/>
       <c r="D64" s="2" t="s">
         <v>20</v>
       </c>
@@ -8447,11 +8448,11 @@
       <c r="L64" s="2"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="42"/>
+      <c r="A65" s="41"/>
       <c r="B65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C65" s="45" t="s">
+      <c r="C65" s="44" t="s">
         <v>43</v>
       </c>
       <c r="D65" s="2" t="s">
@@ -8481,11 +8482,11 @@
       <c r="L65" s="2"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="42"/>
+      <c r="A66" s="41"/>
       <c r="B66" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C66" s="46"/>
+      <c r="C66" s="45"/>
       <c r="D66" s="2" t="s">
         <v>20</v>
       </c>
@@ -8513,11 +8514,11 @@
       <c r="L66" s="2"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="43"/>
+      <c r="A67" s="42"/>
       <c r="B67" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="47"/>
+      <c r="C67" s="46"/>
       <c r="D67" s="2" t="s">
         <v>20</v>
       </c>
@@ -8545,13 +8546,13 @@
       <c r="L67" s="2"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="41" t="s">
+      <c r="A68" s="40" t="s">
         <v>71</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C68" s="45" t="s">
+      <c r="C68" s="44" t="s">
         <v>72</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -8581,11 +8582,11 @@
       <c r="L68" s="2"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="42"/>
+      <c r="A69" s="41"/>
       <c r="B69" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="46"/>
+      <c r="C69" s="45"/>
       <c r="D69" s="2" t="s">
         <v>11</v>
       </c>
@@ -8613,11 +8614,11 @@
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="42"/>
+      <c r="A70" s="41"/>
       <c r="B70" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C70" s="47"/>
+      <c r="C70" s="46"/>
       <c r="D70" s="2" t="s">
         <v>11</v>
       </c>
@@ -8645,11 +8646,11 @@
       <c r="L70" s="2"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="42"/>
+      <c r="A71" s="41"/>
       <c r="B71" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C71" s="45">
+      <c r="C71" s="44">
         <v>2050</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -8679,11 +8680,11 @@
       <c r="L71" s="2"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="42"/>
+      <c r="A72" s="41"/>
       <c r="B72" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="46"/>
+      <c r="C72" s="45"/>
       <c r="D72" s="2" t="s">
         <v>11</v>
       </c>
@@ -8711,11 +8712,11 @@
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="43"/>
+      <c r="A73" s="42"/>
       <c r="B73" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C73" s="47"/>
+      <c r="C73" s="46"/>
       <c r="D73" s="2" t="s">
         <v>11</v>
       </c>
@@ -8743,13 +8744,13 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="40" t="s">
+      <c r="A74" s="43" t="s">
         <v>44</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="45" t="s">
+      <c r="C74" s="44" t="s">
         <v>41</v>
       </c>
       <c r="D74" s="2" t="s">
@@ -8779,11 +8780,11 @@
       <c r="L74" s="2"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="40"/>
+      <c r="A75" s="43"/>
       <c r="B75" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="46"/>
+      <c r="C75" s="45"/>
       <c r="D75" s="2" t="s">
         <v>24</v>
       </c>
@@ -8811,11 +8812,11 @@
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="40"/>
+      <c r="A76" s="43"/>
       <c r="B76" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C76" s="47"/>
+      <c r="C76" s="46"/>
       <c r="D76" s="2" t="s">
         <v>24</v>
       </c>
@@ -8843,11 +8844,11 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="40"/>
+      <c r="A77" s="43"/>
       <c r="B77" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C77" s="45" t="s">
+      <c r="C77" s="44" t="s">
         <v>42</v>
       </c>
       <c r="D77" s="2" t="s">
@@ -8877,11 +8878,11 @@
       <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="40"/>
+      <c r="A78" s="43"/>
       <c r="B78" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="46"/>
+      <c r="C78" s="45"/>
       <c r="D78" s="2" t="s">
         <v>24</v>
       </c>
@@ -8909,11 +8910,11 @@
       <c r="L78" s="2"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="40"/>
+      <c r="A79" s="43"/>
       <c r="B79" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C79" s="47"/>
+      <c r="C79" s="46"/>
       <c r="D79" s="2" t="s">
         <v>24</v>
       </c>
@@ -8961,35 +8962,44 @@
       <c r="F84" s="25"/>
     </row>
     <row r="85" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E85" s="56"/>
+      <c r="E85" s="49"/>
       <c r="F85" s="25"/>
     </row>
     <row r="86" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E86" s="54"/>
+      <c r="E86" s="50"/>
       <c r="F86" s="25"/>
     </row>
     <row r="87" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E87" s="54"/>
+      <c r="E87" s="50"/>
       <c r="F87" s="25"/>
     </row>
     <row r="88" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E88" s="54"/>
+      <c r="E88" s="50"/>
       <c r="F88" s="25"/>
     </row>
     <row r="89" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E89" s="54"/>
+      <c r="E89" s="50"/>
       <c r="F89" s="25"/>
     </row>
     <row r="90" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E90" s="55"/>
+      <c r="E90" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="C29:C34"/>
+    <mergeCell ref="A45:C46"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="C23:C28"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C22"/>
     <mergeCell ref="A2:A34"/>
     <mergeCell ref="M51:M53"/>
     <mergeCell ref="E85:E90"/>
@@ -9006,20 +9016,11 @@
     <mergeCell ref="C68:C70"/>
     <mergeCell ref="M54:M56"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="C23:C28"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="C29:C34"/>
-    <mergeCell ref="A45:C46"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="D32:D34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9082,113 +9083,113 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="43" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="42"/>
-      <c r="B15" s="40"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="43"/>
       <c r="C15" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="42"/>
-      <c r="B16" s="40"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="43"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
-      <c r="B17" s="40" t="s">
+      <c r="A17" s="41"/>
+      <c r="B17" s="43" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="43"/>
       <c r="C18" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="43"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="56" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="42"/>
-      <c r="B21" s="44"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="56"/>
       <c r="C21" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="42"/>
-      <c r="B22" s="44"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="56"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="42"/>
-      <c r="B23" s="40">
+      <c r="A23" s="41"/>
+      <c r="B23" s="43">
         <v>2050</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="42"/>
-      <c r="B24" s="40"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="43"/>
       <c r="C24" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="43"/>
-      <c r="B25" s="40"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="43" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
-      <c r="B27" s="40"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
       <c r="C27" s="20" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="40"/>
-      <c r="B28" s="40"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
       <c r="C28" s="20"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
-      <c r="B29" s="40" t="s">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="40"/>
-      <c r="B30" s="40"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
       <c r="C30" s="20" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
-      <c r="B31" s="40"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="39" t="s">
@@ -9199,146 +9200,151 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="40" t="s">
+      <c r="A35" s="43" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="40"/>
+      <c r="A36" s="43"/>
       <c r="B36" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="40"/>
+      <c r="A37" s="43"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="40" t="s">
+      <c r="A38" s="43" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+      <c r="A39" s="43"/>
       <c r="B39" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="40"/>
+      <c r="A40" s="43"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="40" t="s">
+      <c r="A41" s="43" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="40"/>
+      <c r="A42" s="43"/>
       <c r="B42" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="40"/>
+      <c r="A43" s="43"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="40" t="s">
+      <c r="A44" s="43" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="40"/>
+      <c r="A45" s="43"/>
       <c r="B45" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="40"/>
+      <c r="A46" s="43"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="43" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="40"/>
+      <c r="A48" s="43"/>
       <c r="B48" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="40"/>
+      <c r="A49" s="43"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="41" t="s">
+      <c r="A50" s="40" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="42"/>
+      <c r="A51" s="41"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="42"/>
+      <c r="A52" s="41"/>
       <c r="B52" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="42"/>
+      <c r="A53" s="41"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="42"/>
+      <c r="A54" s="41"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="43"/>
+      <c r="A55" s="42"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="41" t="s">
+      <c r="A56" s="40" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="42"/>
+      <c r="A57" s="41"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="42"/>
+      <c r="A58" s="41"/>
       <c r="B58" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="42"/>
+      <c r="A59" s="41"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="42"/>
+      <c r="A60" s="41"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="43"/>
+      <c r="A61" s="42"/>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="41" t="s">
+      <c r="A62" s="40" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="42"/>
+      <c r="A63" s="41"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="42"/>
+      <c r="A64" s="41"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="42"/>
+      <c r="A65" s="41"/>
       <c r="B65" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="42"/>
+      <c r="A66" s="41"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="43"/>
+      <c r="A67" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="A56:A61"/>
+    <mergeCell ref="A62:A67"/>
     <mergeCell ref="A41:A43"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="B14:B16"/>
@@ -9351,26 +9357,12 @@
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A55"/>
-    <mergeCell ref="A56:A61"/>
-    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004852086843206E4BAD9D3EBF106DD24D" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a9a97e63b44ff58574b9e2ab8e320aec">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="232e48a4-996a-4688-951c-c513fbc1255c" xmlns:ns3="054690b1-a5d8-490b-abb5-be9830757502" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="459ac7c8f33d9cbb3a29af681caa2e24" ns2:_="" ns3:_="">
     <xsd:import namespace="232e48a4-996a-4688-951c-c513fbc1255c"/>
@@ -9637,6 +9629,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9650,14 +9651,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15A8345F-B5BB-4013-8234-B3F44FED454D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63CFF838-52F1-4071-B16F-39CE98ED8A63}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9676,6 +9669,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15A8345F-B5BB-4013-8234-B3F44FED454D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688F3E42-A9A9-4B55-809D-F423D84F64A1}">
   <ds:schemaRefs>
